--- a/out/LSTM-S4_repeat_3_000001.xlsx
+++ b/out/LSTM-S4_repeat_3_000001.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.086732063307571</v>
+        <v>15.28973846592426</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.086732063307571</v>
+        <v>0.1742763026941591</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>2.791318200473974</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>2.791318200473974</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>2.791318200473974</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>2.791318200473974</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>2.791318200473974</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>2.791318200473974</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.4867320633075709</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>2.191318200473975</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>2.191318200473975</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>2.791318200473974</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>2.791318200473974</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>2.791318200473974</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>2.791318200473974</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>2.791318200473974</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>2.791318200473974</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>2.791318200473974</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>2.191318200473975</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>2.191318200473975</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>2.191318200473975</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>2.191318200473975</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>2.191318200473975</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>2.191318200473975</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>2.191318200473975</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>2.191318200473975</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>2.191318200473975</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34327,14 +34327,14 @@
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>2.191318200473975</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.191318200473975</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC43" t="n">
-        <v>-0.0002789766712053679</v>
+        <v>-6.522884500527289e-05</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.1201192548367894</v>
+        <v>0.02808564681070064</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.191318200473975</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.2405590762062427</v>
+        <v>0.05624624678713619</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.4640842068941572</v>
+        <v>0.1085088794383322</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>2.191318200473975</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC45" t="n">
-        <v>1.048915410845982</v>
+        <v>0.2452518374137715</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.1427543945511352</v>
+        <v>0.03337793958473097</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>2.191318200473975</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.8697535207720735</v>
+        <v>0.2033608363725715</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.02896613511877654</v>
+        <v>0.006772323509422399</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>2.191318200473975</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.7847070512155213</v>
+        <v>0.1834748228730182</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.02508596035153532</v>
+        <v>0.005863566622783443</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.805880814347805</v>
+        <v>0.1884236426376505</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.01226360685219675</v>
+        <v>0.002863672648104922</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.8052904096363319</v>
+        <v>0.1882820691942722</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.005850855999743503</v>
+        <v>0.001364083631158653</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.8047142359409569</v>
+        <v>0.188143505866406</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.002434504109724218</v>
+        <v>0.0005656279581166873</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.8037255535344209</v>
+        <v>0.187908437385919</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.001685732234647233</v>
+        <v>0.0003900958028933744</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.8046605202661679</v>
+        <v>0.1881232567927102</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0007011385779361524</v>
+        <v>0.0001599374780580794</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.8043744547373026</v>
+        <v>0.1880524789126902</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0003611580428867456</v>
+        <v>8.052596622172162e-05</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.8043948963185502</v>
+        <v>0.1880534453850971</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0001388127596873637</v>
+        <v>2.859130153281488e-05</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.8043109329302425</v>
+        <v>0.1880298579022884</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>7.345075680301679e-05</v>
+        <v>1.332426436274844e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.8043188612905764</v>
+        <v>0.1880279254918529</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>3.339767778880302e-05</v>
+        <v>4.034747715012475e-06</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.8043126824843665</v>
+        <v>0.1880226420301429</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>1.311607093032661e-05</v>
+        <v>-7.373950752172664e-07</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.8043054403800436</v>
+        <v>0.1880170900940134</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>2.839921505579082e-06</v>
+        <v>-3.155312586922569e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.8042979099076556</v>
+        <v>0.1880114398288601</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-1.279375894546688e-06</v>
+        <v>-4.173194643232597e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.8042920391813514</v>
+        <v>0.1880061985075593</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-3.728542685550439e-06</v>
+        <v>-4.68213567138761e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.8042861743853502</v>
+        <v>0.1880009105687088</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-4.634963333793937e-06</v>
+        <v>-4.817481666896968e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.804280495208642</v>
+        <v>0.1879956387346578</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-4.777674021158921e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.8042756139103926</v>
+        <v>0.1879956785901301</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>-4.737866375420875e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.8042706927088448</v>
+        <v>0.1879957184456023</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.8042706847377503</v>
+        <v>0.1879957104745079</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.8042708441596395</v>
+        <v>0.187995869896397</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.8042707485065059</v>
+        <v>0.1879957742432635</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.8042710992346622</v>
+        <v>0.1879961249714198</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.8042708521307339</v>
+        <v>0.1879958778674914</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.8042708122752616</v>
+        <v>0.1879958380120192</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.8042707485065059</v>
+        <v>0.1879957742432635</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.8042708202463561</v>
+        <v>0.1879958459831136</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.8042707485065059</v>
+        <v>0.1879957742432635</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.8042708521307339</v>
+        <v>0.1879958778674914</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.8042709477838675</v>
+        <v>0.1879959735206251</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.8042708840151117</v>
+        <v>0.1879959097518693</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.8042708441596395</v>
+        <v>0.187995869896397</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.8042708202463561</v>
+        <v>0.1879958459831136</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.804270573142428</v>
+        <v>0.1879955988791855</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.8042704934314832</v>
+        <v>0.1879955191682407</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.8042705412580499</v>
+        <v>0.1879955669948075</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.804270660824467</v>
+        <v>0.1879956865612245</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.8042706448822781</v>
+        <v>0.1879956706190356</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.804270660824467</v>
+        <v>0.1879956865612245</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.8042706448822781</v>
+        <v>0.1879956706190356</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.8042707006799392</v>
+        <v>0.1879957264166968</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.8042707006799392</v>
+        <v>0.1879957264166968</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.8042707006799392</v>
+        <v>0.1879957264166968</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.8042708521307339</v>
+        <v>0.1879958778674914</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.8042710673502844</v>
+        <v>0.187996093087042</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.8042709796682455</v>
+        <v>0.187996005405003</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.8042709318416786</v>
+        <v>0.1879959575784362</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.8042709796682455</v>
+        <v>0.187996005405003</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.8042707963330727</v>
+        <v>0.1879958220698303</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.8042708043041672</v>
+        <v>0.1879958300409247</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.8042708122752616</v>
+        <v>0.1879958380120192</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.8042708202463561</v>
+        <v>0.1879958459831136</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.8042708202463561</v>
+        <v>0.1879958459831136</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.8042708601018284</v>
+        <v>0.1879958858385859</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.8042709238705842</v>
+        <v>0.1879959496073418</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.8042710354659066</v>
+        <v>0.1879960612026642</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.8042710832924733</v>
+        <v>0.1879961090292309</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.8042710434370011</v>
+        <v>0.1879960691737586</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.804270971697151</v>
+        <v>0.1879959974339085</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.8042710912635678</v>
+        <v>0.1879961170003253</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.8042709318416786</v>
+        <v>0.1879959575784362</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.8042707006799392</v>
+        <v>0.1879957264166968</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.8042706528533725</v>
+        <v>0.1879956785901301</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.8042706847377503</v>
+        <v>0.1879957104745079</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.8042707485065059</v>
+        <v>0.1879957742432635</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.8042707485065059</v>
+        <v>0.1879957742432635</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.8042706687955614</v>
+        <v>0.187995694532319</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.8042705492291443</v>
+        <v>0.1879955749659019</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.8042705093736721</v>
+        <v>0.1879955351104296</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.8042706528533725</v>
+        <v>0.1879956785901301</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.8042707883619783</v>
+        <v>0.1879958140987358</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.8042707724197894</v>
+        <v>0.1879957981565469</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.8042707485065059</v>
+        <v>0.1879957742432635</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.8042707086510337</v>
+        <v>0.1879957343877912</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.8042706050268058</v>
+        <v>0.1879956307635633</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.8042704854603887</v>
+        <v>0.1879955111971462</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.8042706050268058</v>
+        <v>0.1879956307635633</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.8042706528533725</v>
+        <v>0.1879956785901301</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.8042707485065059</v>
+        <v>0.1879957742432635</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.8042706289400892</v>
+        <v>0.1879956546768467</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.8042706369111836</v>
+        <v>0.1879956626479412</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-S4_repeat_3_000001.xlsx
+++ b/out/LSTM-S4_repeat_3_000001.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394772</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394772</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394772</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394772</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394772</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394772</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394772</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394772</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394772</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394772</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394772</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394772</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA14" t="n">
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.086732063307571</v>
+        <v>0.3697952168820189</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>2.791318200473974</v>
+        <v>1.119063848603515</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>2.791318200473974</v>
+        <v>1.868332480325011</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>2.791318200473974</v>
+        <v>1.868332480325011</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>2.791318200473974</v>
+        <v>1.868332480325011</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>2.791318200473974</v>
+        <v>1.868332480325011</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>2.791318200473974</v>
+        <v>1.119063848603515</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA21" t="n">
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.4867320633075709</v>
+        <v>0.3697952168820189</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394772</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA23" t="n">
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.086732063307571</v>
+        <v>0.1697952168820188</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>2.191318200473975</v>
+        <v>0.9190638486035149</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>2.191318200473975</v>
+        <v>1.668332480325011</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>2.791318200473974</v>
+        <v>1.868332480325011</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>2.791318200473974</v>
+        <v>1.868332480325011</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>2.791318200473974</v>
+        <v>1.868332480325011</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>2.791318200473974</v>
+        <v>1.868332480325011</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>2.791318200473974</v>
+        <v>1.868332480325011</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>2.791318200473974</v>
+        <v>1.868332480325011</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>2.791318200473974</v>
+        <v>1.868332480325011</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>2.191318200473975</v>
+        <v>1.868332480325011</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>2.191318200473975</v>
+        <v>1.668332480325011</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>2.191318200473975</v>
+        <v>1.668332480325011</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>2.191318200473975</v>
+        <v>1.668332480325011</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>2.191318200473975</v>
+        <v>1.668332480325011</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>2.191318200473975</v>
+        <v>1.668332480325011</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>2.191318200473975</v>
+        <v>1.668332480325011</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>2.191318200473975</v>
+        <v>1.668332480325011</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>2.191318200473975</v>
+        <v>1.668332480325011</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>2.191318200473975</v>
+        <v>1.668332480325011</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,10 +35129,10 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.191318200473975</v>
+        <v>1.668332480325011</v>
       </c>
       <c r="JC43" t="n">
-        <v>-0.0002789766712053679</v>
+        <v>-0.0002362617722647265</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.1201192548367894</v>
+        <v>0.1017273524582474</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.191318200473975</v>
+        <v>1.668332480325011</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.2405590762062427</v>
+        <v>0.203726403295239</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.4640842068941572</v>
+        <v>0.3930273887656089</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>2.191318200473975</v>
+        <v>1.668332480325011</v>
       </c>
       <c r="JC45" t="n">
-        <v>1.048915410845982</v>
+        <v>0.8883137576502087</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.1427543945511352</v>
+        <v>0.1208974279825509</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>2.191318200473975</v>
+        <v>1.668332480325011</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.8697535207720735</v>
+        <v>0.7365836853414094</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.02896613511877654</v>
+        <v>0.02453078088659488</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>2.191318200473975</v>
+        <v>0.9190638486035149</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.7847070512155213</v>
+        <v>0.6645591004566068</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.02508596035153532</v>
+        <v>0.02124474646651829</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.086732063307571</v>
+        <v>0.1697952168820188</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.805880814347805</v>
+        <v>0.6824909962963934</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.01226360685219675</v>
+        <v>0.01038642421958356</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394772</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.8052904096363319</v>
+        <v>0.681990977966862</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.005850855999743503</v>
+        <v>0.00495416969763764</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394772</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.8047142359409569</v>
+        <v>0.6815022611759095</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.002434504109724218</v>
+        <v>0.002060951563483928</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394772</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.8037255535344209</v>
+        <v>0.680664189452697</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.001685732234647233</v>
+        <v>0.001427222285488482</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394772</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.8046605202661679</v>
+        <v>0.6814552546314451</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0007011385779361524</v>
+        <v>0.0005928983579605377</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394772</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.8043744547373026</v>
+        <v>0.6812122721398512</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0003611580428867456</v>
+        <v>0.0003050316275537409</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394772</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.8043948963185502</v>
+        <v>0.6812288139166737</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0001388127596873637</v>
+        <v>0.0001167684680564539</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394772</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.8043109329302425</v>
+        <v>0.6811569544054058</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>7.345075680301679e-05</v>
+        <v>6.14254583149631e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394772</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.8043188612905764</v>
+        <v>0.6811629010462724</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>3.339767778880302e-05</v>
+        <v>2.775096046692022e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394772</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.8043126824843665</v>
+        <v>0.6811569023927916</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>1.311607093032661e-05</v>
+        <v>1.045194285233741e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394772</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.8043054403800436</v>
+        <v>0.6811500172051913</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>2.839921505579082e-06</v>
+        <v>1.456405945771008e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394772</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.8042979099076556</v>
+        <v>0.6811429206267805</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-1.279375894546688e-06</v>
+        <v>-2.106181251314092e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394772</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.8042920391813514</v>
+        <v>0.6811371955686439</v>
       </c>
     </row>
     <row r="61">
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394772</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.8042861743853502</v>
+        <v>0.6811314264257764</v>
       </c>
     </row>
     <row r="62">
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394772</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.804280495208642</v>
+        <v>0.6811258827576739</v>
       </c>
     </row>
     <row r="63">
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394772</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.8042756139103926</v>
+        <v>0.6811209616039525</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>-4.737866375420875e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394772</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.8042706927088448</v>
+        <v>0.6811210014594249</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394772</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.8042706847377503</v>
+        <v>0.6811209934883304</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394772</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.8042708441596395</v>
+        <v>0.6811211529102195</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394772</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.8042707485065059</v>
+        <v>0.681121057257086</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394772</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.8042710992346622</v>
+        <v>0.6811214079852423</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394772</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.8042708521307339</v>
+        <v>0.6811211608813139</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394772</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.8042708122752616</v>
+        <v>0.6811211210258417</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394772</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.8042707485065059</v>
+        <v>0.681121057257086</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394772</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.8042708202463561</v>
+        <v>0.6811211289969361</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394772</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.8042707485065059</v>
+        <v>0.681121057257086</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394772</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.8042708521307339</v>
+        <v>0.6811211608813139</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394772</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.8042709477838675</v>
+        <v>0.6811212565344477</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394772</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.8042708840151117</v>
+        <v>0.6811211927656918</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394772</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.8042708441596395</v>
+        <v>0.6811211529102195</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394772</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.8042708202463561</v>
+        <v>0.6811211289969361</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394772</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.804270573142428</v>
+        <v>0.681120881893008</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394772</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.8042704934314832</v>
+        <v>0.6811208021820633</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394772</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.8042705412580499</v>
+        <v>0.68112085000863</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394772</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.804270660824467</v>
+        <v>0.681120969575047</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394772</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.8042706448822781</v>
+        <v>0.6811209536328581</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394772</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.804270660824467</v>
+        <v>0.681120969575047</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394772</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.8042706448822781</v>
+        <v>0.6811209536328581</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394772</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.8042707006799392</v>
+        <v>0.6811210094305193</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394772</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.8042707006799392</v>
+        <v>0.6811210094305193</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394772</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.8042707006799392</v>
+        <v>0.6811210094305193</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394772</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.8042708521307339</v>
+        <v>0.6811211608813139</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394772</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.8042710673502844</v>
+        <v>0.6811213761008645</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394772</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.8042709796682455</v>
+        <v>0.6811212884188255</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394772</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.8042709318416786</v>
+        <v>0.6811212405922588</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394772</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.8042709796682455</v>
+        <v>0.6811212884188255</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394772</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.8042707963330727</v>
+        <v>0.6811211050836528</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394772</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.8042708043041672</v>
+        <v>0.6811211130547472</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394772</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.8042708122752616</v>
+        <v>0.6811211210258417</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394772</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.8042708202463561</v>
+        <v>0.6811211289969361</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394772</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.8042708202463561</v>
+        <v>0.6811211289969361</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394772</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.8042708601018284</v>
+        <v>0.6811211688524084</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394772</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.8042709238705842</v>
+        <v>0.6811212326211643</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394772</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.8042710354659066</v>
+        <v>0.6811213442164866</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394772</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.8042710832924733</v>
+        <v>0.6811213920430534</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394772</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.8042710434370011</v>
+        <v>0.6811213521875811</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394772</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.804270971697151</v>
+        <v>0.681121280447731</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394772</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.8042710912635678</v>
+        <v>0.6811214000141479</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394772</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.8042709318416786</v>
+        <v>0.6811212405922588</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394772</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.8042707006799392</v>
+        <v>0.6811210094305193</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394772</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.8042706528533725</v>
+        <v>0.6811209616039525</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394772</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.8042706847377503</v>
+        <v>0.6811209934883304</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394772</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.8042707485065059</v>
+        <v>0.681121057257086</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394772</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.8042707485065059</v>
+        <v>0.681121057257086</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394772</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.8042706687955614</v>
+        <v>0.6811209775461415</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394772</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.8042705492291443</v>
+        <v>0.6811208579797244</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394772</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.8042705093736721</v>
+        <v>0.6811208181242522</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394772</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.8042706528533725</v>
+        <v>0.6811209616039525</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394772</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.8042707883619783</v>
+        <v>0.6811210971125583</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394772</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.8042707724197894</v>
+        <v>0.6811210811703694</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394772</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.8042707485065059</v>
+        <v>0.681121057257086</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394772</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.8042707086510337</v>
+        <v>0.6811210174016138</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394772</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.8042706050268058</v>
+        <v>0.6811209137773858</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394772</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.8042704854603887</v>
+        <v>0.6811207942109688</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394772</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.8042706050268058</v>
+        <v>0.6811209137773858</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394772</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.8042706528533725</v>
+        <v>0.6811209616039525</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394772</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.8042707485065059</v>
+        <v>0.681121057257086</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394772</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.8042706289400892</v>
+        <v>0.6811209376906692</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394772</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.8042706369111836</v>
+        <v>0.6811209456617636</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-S4_repeat_3_000001.xlsx
+++ b/out/LSTM-S4_repeat_3_000001.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.006708964705467224</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.5794734148394772</v>
+        <v>-1.14</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>-0.004044558852910995</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.5794734148394772</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>-0.002976223826408386</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.5794734148394772</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>-0.002636495977640152</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.5794734148394772</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>-0.002213500440120697</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.5794734148394772</v>
+        <v>-0.3</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>-0.001383688300848007</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.5794734148394772</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>-0.00141417607665062</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.5794734148394772</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>-0.001408424228429794</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.5794734148394772</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>-0.00101201981306076</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.5794734148394772</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>-0.001098934561014175</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.5794734148394772</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>-0.0009534507989883423</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.5794734148394772</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>-0.0007263906300067902</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.5794734148394772</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>-0.0001855641603469849</v>
       </c>
       <c r="JB14" t="n">
-        <v>0.3697952168820189</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0.0005746930837631226</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.119063848603515</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0.001074962317943573</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.868332480325011</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0.001180566847324371</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.868332480325011</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0.000593382865190506</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.868332480325011</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0.0002293102443218231</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.868332480325011</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>7.833540439605713e-05</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.119063848603515</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>-0.0001833885908126831</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.3697952168820189</v>
+        <v>-0.16</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>-0.000350169837474823</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.5794734148394772</v>
+        <v>-0.3</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>-0.0002240985631942749</v>
       </c>
       <c r="JB23" t="n">
-        <v>0.1697952168820188</v>
+        <v>-0.16</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>9.315460920333862e-05</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.9190638486035149</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.0005197636783123016</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.668332480325011</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0.0004624053835868835</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.868332480325011</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.0002382248640060425</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.868332480325011</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.000111900269985199</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.868332480325011</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>5.19677996635437e-05</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.868332480325011</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0.0005212314426898956</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.868332480325011</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.001234758645296097</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.868332480325011</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.001011773943901062</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.868332480325011</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0.0008822046220302582</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.868332480325011</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0.00059480220079422</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.668332480325011</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.0006096325814723969</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.668332480325011</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.0005030408501625061</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.668332480325011</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.0006919205188751221</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.668332480325011</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.0009531453251838684</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.668332480325011</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.001199539750814438</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.668332480325011</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.002275753766298294</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.668332480325011</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.003240659832954407</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.668332480325011</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.004383154213428497</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.668332480325011</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.005074143409729004</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.668332480325011</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
-        <v>-0.0002362617722647265</v>
+        <v>-0.0001816752822221024</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.1017273524582474</v>
+        <v>0.07822410178061202</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.006080649793148041</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.668332480325011</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.203726403295239</v>
+        <v>0.1566569630070983</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.3930273887656089</v>
+        <v>0.3022210742498265</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.006017014384269714</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.668332480325011</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.8883137576502087</v>
+        <v>0.6830750487817598</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.1208974279825509</v>
+        <v>0.09296489660347235</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.003082834184169769</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.668332480325011</v>
+        <v>-0.3</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.7365836853414094</v>
+        <v>0.5664011813620098</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.02453078088659488</v>
+        <v>0.01886306248949166</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.000401761382818222</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.9190638486035149</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.6645591004566068</v>
+        <v>0.5110173888417329</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.02124474646651829</v>
+        <v>0.01633660823303623</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>-0.002360735088586807</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.1697952168820188</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.6824909962963934</v>
+        <v>0.5248062758631562</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.01038642421958356</v>
+        <v>0.007985702361668543</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>-0.003336939960718155</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.5794734148394772</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.681990977966862</v>
+        <v>0.524420894243811</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.00495416969763764</v>
+        <v>0.003808255384588791</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>-0.003854569047689438</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.5794734148394772</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.6815022611759095</v>
+        <v>0.5240439424238605</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.002060951563483928</v>
+        <v>0.001583850919478074</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>-0.003808524459600449</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.5794734148394772</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.680664189452697</v>
+        <v>0.5233983419913631</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.001427222285488482</v>
+        <v>0.001096175216267276</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>-0.003842782229185104</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.5794734148394772</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.6814552546314451</v>
+        <v>0.5240054028804111</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0005928983579605377</v>
+        <v>0.0004543766478726977</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>-0.003052923828363419</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.5794734148394772</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.6812122721398512</v>
+        <v>0.5238174288811471</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0003050316275537409</v>
+        <v>0.0002335372651652704</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>-0.002607833594083786</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.5794734148394772</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.6812288139166737</v>
+        <v>0.5238290030499527</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0001167684680564539</v>
+        <v>8.842580738814138e-05</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>-0.003551196306943893</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.5794734148394772</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.6811569544054058</v>
+        <v>0.5237725621866074</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>6.14254583149631e-05</v>
+        <v>4.596436025889411e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>-0.004473574459552765</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.5794734148394772</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.6811629010462724</v>
+        <v>0.5237760087290115</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>2.775096046692022e-05</v>
+        <v>2.041022794847258e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>-0.00561252236366272</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.5794734148394772</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.6811569023927916</v>
+        <v>0.5237702339116556</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>1.045194285233741e-05</v>
+        <v>6.722163543152517e-06</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>-0.006039585918188095</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.5794734148394772</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.6811500172051913</v>
+        <v>0.5237637718849604</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>1.456405945771008e-06</v>
+        <v>7.289038596293463e-08</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>-0.006043963134288788</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.5794734148394772</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.6811429206267805</v>
+        <v>0.5237571092005268</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-2.106181251314092e-06</v>
+        <v>-2.519583929697793e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>-0.005799043923616409</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.5794734148394772</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.6811371955686439</v>
+        <v>0.5237515287163241</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-3.728542685550439e-06</v>
+        <v>-4.04640701416283e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.005342680960893631</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.5794734148394772</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.6811314264257764</v>
+        <v>0.5237459518591734</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-4.634963333793937e-06</v>
+        <v>-4.817481666896968e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>-0.005114596337080002</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.5794734148394772</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.6811258827576739</v>
+        <v>0.5237405445165164</v>
       </c>
     </row>
     <row r="63">
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.004583045840263367</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.5794734148394772</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.6811209616039525</v>
+        <v>0.523735623362795</v>
       </c>
     </row>
     <row r="64">
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.004721309989690781</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.5794734148394772</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.6811210014594249</v>
+        <v>0.5237356632182673</v>
       </c>
     </row>
     <row r="65">
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>-0.004488050937652588</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.5794734148394772</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.6811209934883304</v>
+        <v>0.5237356552471728</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>-0.004682887345552444</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.5794734148394772</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.6811211529102195</v>
+        <v>0.5237358146690619</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>-0.004064496606588364</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.5794734148394772</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.681121057257086</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-0.004083059728145599</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.5794734148394772</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.6811214079852423</v>
+        <v>0.5237360697440847</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.004677295684814453</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.5794734148394772</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.6811211608813139</v>
+        <v>0.5237358226401564</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.004700548946857452</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.5794734148394772</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.6811211210258417</v>
+        <v>0.5237357827846841</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-0.005027629435062408</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.5794734148394772</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.681121057257086</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.005149323493242264</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.5794734148394772</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.6811211289969361</v>
+        <v>0.5237357907557786</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.005062788724899292</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.5794734148394772</v>
+        <v>0.16</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.681121057257086</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>-0.002777379006147385</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.5794734148394772</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.6811211608813139</v>
+        <v>0.5237358226401564</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.002765282988548279</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.5794734148394772</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.6811212565344477</v>
+        <v>0.52373591829329</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>-0.003984894603490829</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.5794734148394772</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.6811211927656918</v>
+        <v>0.5237358545245342</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>-0.004943236708641052</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.5794734148394772</v>
+        <v>0.16</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.6811211529102195</v>
+        <v>0.5237358146690619</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.004937570542097092</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.5794734148394772</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.6811211289969361</v>
+        <v>0.5237357907557786</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.004895664751529694</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.5794734148394772</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.681120881893008</v>
+        <v>0.5237355436518504</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>-0.00461970642209053</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.5794734148394772</v>
+        <v>-0.3</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.6811208021820633</v>
+        <v>0.5237354639409056</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>-0.003969181329011917</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.5794734148394772</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.68112085000863</v>
+        <v>0.5237355117674724</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>-0.003697644919157028</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.5794734148394772</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.681120969575047</v>
+        <v>0.5237356313338895</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>-0.003340750932693481</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.5794734148394772</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.6811209536328581</v>
+        <v>0.5237356153917005</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>-0.003171596676111221</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.5794734148394772</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.681120969575047</v>
+        <v>0.5237356313338895</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>-0.003269527107477188</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.5794734148394772</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.6811209536328581</v>
+        <v>0.5237356153917005</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>-0.003736894577741623</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.5794734148394772</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.6811210094305193</v>
+        <v>0.5237356711893617</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>-0.004379712045192719</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.5794734148394772</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.6811210094305193</v>
+        <v>0.5237356711893617</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>-0.003908276557922363</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.5794734148394772</v>
+        <v>-0.16</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.6811210094305193</v>
+        <v>0.5237356711893617</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>-0.004364240914583206</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.5794734148394772</v>
+        <v>-0.3</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.6811211608813139</v>
+        <v>0.5237358226401564</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>-0.003697734326124191</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.5794734148394772</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.6811213761008645</v>
+        <v>0.5237360378597069</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>-0.004226882010698318</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.5794734148394772</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.6811212884188255</v>
+        <v>0.5237359501776679</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>-0.004472613334655762</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.5794734148394772</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.6811212405922588</v>
+        <v>0.5237359023511011</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>-0.004265271127223969</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.5794734148394772</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.6811212884188255</v>
+        <v>0.5237359501776679</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>-0.004322506487369537</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.5794734148394772</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.6811211050836528</v>
+        <v>0.5237357668424952</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>-0.004178814589977264</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.5794734148394772</v>
+        <v>-0.16</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.6811211130547472</v>
+        <v>0.5237357748135897</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>-0.003670219331979752</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.5794734148394772</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.6811211210258417</v>
+        <v>0.5237357827846841</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>-0.003374967724084854</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.5794734148394772</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.6811211289969361</v>
+        <v>0.5237357907557786</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>-0.003009967505931854</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.5794734148394772</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.6811211289969361</v>
+        <v>0.5237357907557786</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-0.001860607415437698</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.5794734148394772</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.6811211688524084</v>
+        <v>0.5237358306112508</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>-0.001338671892881393</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.5794734148394772</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.6811212326211643</v>
+        <v>0.5237358943800067</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>-0.001175090670585632</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.5794734148394772</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.6811213442164866</v>
+        <v>0.5237360059753291</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>-0.001707464456558228</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.5794734148394772</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.6811213920430534</v>
+        <v>0.5237360538018958</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>-0.002016104757785797</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.5794734148394772</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.6811213521875811</v>
+        <v>0.5237360139464236</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>-0.00207877904176712</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.5794734148394772</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.681121280447731</v>
+        <v>0.5237359422065735</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.002186667174100876</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.5794734148394772</v>
+        <v>-0.16</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.6811214000141479</v>
+        <v>0.5237360617729903</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>-0.002168882638216019</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.5794734148394772</v>
+        <v>-0.3</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.6811212405922588</v>
+        <v>0.5237359023511011</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.00271095335483551</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.5794734148394772</v>
+        <v>-0.3</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.6811210094305193</v>
+        <v>0.5237356711893617</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-0.002907536923885345</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.5794734148394772</v>
+        <v>-0.3</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.6811209616039525</v>
+        <v>0.523735623362795</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>-0.003072649240493774</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.5794734148394772</v>
+        <v>-0.3</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.6811209934883304</v>
+        <v>0.5237356552471728</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>-0.002720233052968979</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.5794734148394772</v>
+        <v>-0.3</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.681121057257086</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>-0.002662960439920425</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.5794734148394772</v>
+        <v>-0.16</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.681121057257086</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>-0.002736039459705353</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.5794734148394772</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.6811209775461415</v>
+        <v>0.5237356393049839</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>-0.002733644098043442</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.5794734148394772</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.6811208579797244</v>
+        <v>0.5237355197385668</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>-0.002754297107458115</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.5794734148394772</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.6811208181242522</v>
+        <v>0.5237354798830945</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>-0.002523072063922882</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.5794734148394772</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.6811209616039525</v>
+        <v>0.523735623362795</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>-0.0025467649102211</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.5794734148394772</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.6811210971125583</v>
+        <v>0.5237357588714008</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>-0.00294850766658783</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.5794734148394772</v>
+        <v>0.3</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.6811210811703694</v>
+        <v>0.5237357429292118</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>-0.003193024545907974</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.5794734148394772</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.681121057257086</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>-0.003200259059667587</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.5794734148394772</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.6811210174016138</v>
+        <v>0.5237356791604562</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>-0.002944450825452805</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.5794734148394772</v>
+        <v>-0.3</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.6811209137773858</v>
+        <v>0.5237355755362283</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>-0.00242629274725914</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.5794734148394772</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.6811207942109688</v>
+        <v>0.5237354559698112</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>-0.002449046820402145</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.5794734148394772</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.6811209137773858</v>
+        <v>0.5237355755362283</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>-0.002290662378072739</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.5794734148394772</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.6811209616039525</v>
+        <v>0.523735623362795</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>-0.002423100173473358</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.5794734148394772</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.681121057257086</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>-0.002461813390254974</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.5794734148394772</v>
+        <v>0.7899999999999999</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.6811209376906692</v>
+        <v>0.5237355994495116</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>-0.002050682902336121</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.5794734148394772</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.6811209456617636</v>
+        <v>0.5237356074206061</v>
       </c>
     </row>
   </sheetData>
